--- a/光伏配储项目/电价数据/2026/镜山站.xlsx
+++ b/光伏配储项目/电价数据/2026/镜山站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.5171399999999999</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.37989</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.95056</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.59842</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.77597</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.64024</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.61276</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43776</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45431</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44054</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42287</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42849</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40845</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39753</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39924</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38393</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40174</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.4229</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.4116</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35353</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39099</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38448</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39252</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.4219</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41296</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42296</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41253</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44395</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.38828</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30378</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33458</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.26191</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.30207</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.32523</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.50713</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.4457</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.26162</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.17498</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.23578</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.27602</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.30207</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.1025</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.20126</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.40868</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.40334</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.19446</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.01697</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.25339</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.09117</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.19046</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.24595</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.27115</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.24671</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.47437</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.34583</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.07631</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.30501</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.17281</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.40032</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.41393</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.497</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.44232</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.42095</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.58963</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>1.08272</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>1.16747</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>1.12513</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.50722</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.8934299999999999</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.6524800000000001</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.53965</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.62766</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.75883</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.69088</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.9849</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.13149</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.84211</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.87459</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.23524</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.63654</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.9264</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.7759299999999999</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.59742</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.8966799999999999</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.81884</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.85921</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.83251</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.5787100000000001</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47943</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40178</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41307</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42232</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.8658400000000001</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.84184</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.8795299999999999</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53607</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.52249</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5062300000000001</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.53738</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.49799</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.41198</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47258</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38938</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38088</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39201</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33759</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37074</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35597</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35958</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37549</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37546</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38044</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42122</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.52097</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.65613</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.7241299999999999</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.44124</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.38379</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.44833</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34592</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.60393</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.69341</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.33914</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.43463</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.5376599999999999</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.31856</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.46752</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.38992</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.39505</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.46737</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.68375</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.71972</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>1.00843</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.6427200000000001</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.70675</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.5850299999999999</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.62162</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.98198</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.7331599999999999</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.49725</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.60392</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.29464</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.35741</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.46423</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.36374</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.36572</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.81149</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.58312</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.5134</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.5710499999999999</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.5740499999999999</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.39904</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.42123</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.69098</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.5779500000000001</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.5162599999999999</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.73821</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.52762</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.00298</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.16708</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.08457</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.91664</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.01447</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.99802</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.16389</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.8368</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.91188</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.1567</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.58204</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.36921</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.50697</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.5002</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.6604800000000001</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44075</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43477</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.41814</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33938</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37745</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35456</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33353</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.51561</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.39749</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.50454</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.39794</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40588</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.39563</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38952</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38258</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36187</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43388</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37017</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39347</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36632</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37092</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35325</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.3586</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34854</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36308</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35618</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.3802</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47352</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45011</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44427</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34836</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39704</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35199</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36838</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34681</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.48209</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.41362</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.4495</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.40274</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.36729</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.45764</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.30876</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31209</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.30277</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.34693</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.35225</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.5739099999999999</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.56764</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.8003899999999999</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.44707</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.67238</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.7708700000000001</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.43088</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.42186</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.48208</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.58221</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.55632</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.41622</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.33488</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.34905</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.3269</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.34234</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.5724</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.5767100000000001</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.60004</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.78592</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.18176</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.6746</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.80304</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.20115</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.61709</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.56556</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.48642</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.6008600000000001</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.88122</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.85878</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.79342</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.55072</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.7783300000000001</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.70239</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.9591000000000001</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.6337</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.8964500000000001</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.62662</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.6475</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.6335599999999999</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.65339</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.58738</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.6761699999999999</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.60819</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.5125</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.51703</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.42549</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.35964</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34311</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31991</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.6039800000000001</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.49237</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.36856</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.40317</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.4271</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.41013</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.34917</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.38926</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.32968</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.32332</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46675</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.32547</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.31842</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.31872</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.32825</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.32015</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.30588</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.30531</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.30383</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.30133</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.3026</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.34534</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35781</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.35197</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38918</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.32668</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.31779</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.36324</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34362</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.42724</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35477</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.37524</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.51646</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.49146</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.38721</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.42946</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.51376</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.34706</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.44868</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.77961</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.7192000000000001</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.49866</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.6203500000000001</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.5678799999999999</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.40041</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.29152</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.26614</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.39211</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.34128</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.32766</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.48368</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.7001799999999999</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.29376</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.36681</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.48187</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.46145</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.46839</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.43234</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.44666</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.41135</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.32782</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.72504</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.43257</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.87161</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.42516</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.43069</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.47266</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.43721</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.48069</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.55557</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.54515</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.60122</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.57104</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.82143</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.55664</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.52904</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.46365</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.47649</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.4917</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.49637</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.46689</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.45724</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.39236</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.33273</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.3162</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.39669</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.30106</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.3083399999999999</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31282</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.30047</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.36811</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.40364</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38758</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30685</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31483</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30886</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.30734</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.29344</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30866</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.30685</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.29285</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.29608</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29448</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29509</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29617</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.30139</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29592</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29817</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31255</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30684</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31647</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32443</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33281</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32611</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.2874</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.27201</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.11385</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.11436</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.11651</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.09006</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.08558</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.09659999999999999</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.08818000000000001</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.10692</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.01612</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.02073</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.0245</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.06562999999999999</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.0848</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.0513</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.06372999999999999</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.01141</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.06787</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.01008</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.08234</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.06287</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.01064</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.04206</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.0411</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.03772</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.04638</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.02626</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21063</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.08798</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.0891</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.09237000000000001</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.00355</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.00855</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.04877</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.00704</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.21168</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.11313</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.16917</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.31565</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.34901</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.3277</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.34727</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.34121</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.34306</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.36069</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.37661</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.3449700000000001</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.35756</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.40137</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39299</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.40201</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.3752</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.35203</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39955</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39844</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40988</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46754</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35819</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.45967</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.3447</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.37573</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.75998</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.4949</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.53642</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.45125</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.44693</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.36613</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.36823</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.36488</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33852</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.31577</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32768</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.36415</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.3569</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.35158</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.3464100000000001</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33614</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31889</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.3316</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33635</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32479</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.3056</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32479</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34245</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.13341</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04853</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04659000000000001</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>0.00847</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04527</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04482</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04318</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04173</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.0296</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.12969</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.01161</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.00095</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.01676</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04294</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04285</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04493</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04482</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04486</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.03572</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04229</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.0446</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04213</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04232</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>0.00855</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04451</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04476</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04253</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04346</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.00983</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.008230000000000001</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.04991</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>0.009939999999999999</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>0.008320000000000001</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>0.009779999999999999</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>0.01223</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>0.01272</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.22876</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.187</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.30815</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.31636</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.30682</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.31743</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.3279</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.31083</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.31086</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.3095</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.31225</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.28619</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.31202</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.32182</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.32399</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.32038</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.31236</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31993</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.32786</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.35715</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35314</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36599</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33621</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.33675</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31295</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.4055299999999999</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35054</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32164</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.31011</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31652</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30477</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28729</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29857</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29432</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.29285</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28688</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27789</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27687</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28594</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.19351</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.18149</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.1718</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14841</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16014</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15938</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23743</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21479</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.23882</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.27499</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.29001</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29507</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29583</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28718</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28777</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28741</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27791</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28791</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31441</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.31144</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.38893</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.45364</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.38134</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.35373</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.43571</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.44801</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.51912</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45654</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.4268</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.46949</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.45172</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.48835</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.35457</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.34368</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.32728</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.32716</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.1532</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29343</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31226</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.32252</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31171</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.3309</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.40999</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.37834</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.38684</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.42419</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47943</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.54775</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.7924500000000001</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6512</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.43639</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.5422100000000001</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.82441</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>1.00855</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.5578200000000001</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>1.01348</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.9776699999999999</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.40033</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.44819</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.99191</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.70823</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.31315</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.97124</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.8517</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.4247</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.11784</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.80538</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5303600000000001</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.78773</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7890199999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87859</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.8814299999999999</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.5066700000000001</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.41212</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.4173</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.4654</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.2244</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87937</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55135</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.63942</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54264</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.50259</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45789</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42624</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.44017</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45068</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39254</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45284</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42073</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.4001</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36529</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.3893</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43395</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39062</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.35366</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.34844</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.35344</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40656</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.3554</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.4509</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35596</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39772</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40012</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58936</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42934</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59623</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.59712</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.6614</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.5482</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.45207</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.56678</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.47178</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.9722799999999999</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.69584</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.92423</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.9055</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.91518</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.37058</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.4881</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.36634</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.3795</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.3451</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.43555</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.5024999999999999</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.34363</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.35332</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.47214</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.41938</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.5863700000000001</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.38791</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.39138</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.34527</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.35994</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.36721</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.3744</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.39747</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.36379</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.37014</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.37784</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.35917</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.36858</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.36711</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.35226</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.36527</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.37319</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.39169</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.37096</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.39921</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.38038</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.38022</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.40488</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.38957</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.38553</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.3774</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.36529</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.34594</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.42464</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41257</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45231</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41493</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39145</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.3749</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35327</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.95623</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.47695</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.40772</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.4822</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.5448099999999999</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.39256</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40968</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.39178</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.41438</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.38361</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35377</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38572</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40008</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50007</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.35825</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.3614</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.3698</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.40733</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.38717</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.23103</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.42034</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.40278</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.4387799999999999</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.40264</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.37406</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.38915</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.39872</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.22883</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.31931</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.27872</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.34362</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.29476</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.32316</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.41631</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.5434099999999999</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.44926</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.38508</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.47097</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.40395</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.36781</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.51502</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.38477</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.30857</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.32243</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.33552</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.32974</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29939</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.35276</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.26912</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32298</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.30609</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.35518</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.29409</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.28317</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.34642</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.23465</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.3152</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.29864</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.32313</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.36213</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.00045</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43249</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.29362</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.3606</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32343</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42044</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40172</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59675</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.93676</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.44328</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.19795</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.7036</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7953600000000001</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64979</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.58365</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45044</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50049</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43746</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5005500000000001</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41293</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42803</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45041</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4235</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43412</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42354</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40249</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.5638200000000001</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.37878</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.42225</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.67623</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.50034</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.45548</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.3655</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.5281699999999999</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.37149</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.53324</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.32357</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.8424199999999999</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.698</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.5885499999999999</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.44321</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.31392</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0.75442</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.7543300000000001</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.45464</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.45172</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.43692</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.6500499999999999</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.67938</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.49527</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.28817</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.31973</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.39308</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.4694700000000001</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.36625</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.465</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.42285</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.41758</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.41202</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.41596</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.47168</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.45765</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.4343399999999999</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.47789</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.5015500000000001</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.46326</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.49567</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.44744</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.44994</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.5630499999999999</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.49414</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.50763</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.45739</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.44502</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.7719</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.5744900000000001</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.92455</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.6632</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.5317999999999999</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.48738</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.47971</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.3865</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36958</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33454</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34092</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32955</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32473</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42539</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33943</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34424</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33992</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33595</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32943</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32493</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32413</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32745</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32617</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31601</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32015</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32013</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.3102200000000001</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32513</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31121</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32051</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39151</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37499</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33882</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35489</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.30257</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.34958</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.30897</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.33232</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>0.99041</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.31532</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.26628</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.18345</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.18815</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.19943</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.5862000000000001</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.5931000000000001</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.17276</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.17922</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.1948</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.1919</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.29684</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.20141</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.30798</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.31035</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.18888</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.17956</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.17143</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.17461</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.20369</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.19805</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.18452</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.33506</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.34154</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.40644</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.32797</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.37485</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36154</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.40531</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38491</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.44972</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.39981</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40188</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39772</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.44352</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43992</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43929</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44421</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44427</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40267</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39054</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39772</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36039</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34805</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34934</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5424099999999999</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38908</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46869</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42387</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41594</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37014</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38109</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38021</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39308</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37993</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36988</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38024</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39108</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37024</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38027</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35028</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35527</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34518</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34476</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35517</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37019</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38011</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35994</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33999</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34024</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34032</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.3445</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35155</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.37554</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28931</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31349</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31318</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.31081</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28645</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28575</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.30602</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.26161</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.27076</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.2573</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.22827</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.24807</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29834</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31402</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.29241</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.29524</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30369</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.30392</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.28739</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.26805</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31497</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.31149</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.3166</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30147</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.31295</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.37279</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.45837</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.4281</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.42264</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.48704</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.61313</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.49599</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.38235</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.36269</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.38228</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.47086</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.53615</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.60842</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.6089600000000001</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.48072</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.41369</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.39938</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.3782799999999999</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.36953</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.36258</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41951</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.39233</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.39538</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.39456</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.38479</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.38261</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38031</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36026</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36606</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41861</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37069</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.45231</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38047</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35276</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36022</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34198</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34778</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34917</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34918</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34014</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34138</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34291</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33811</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33806</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33982</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33062</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34177</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.34597</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34945</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.3612</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.39739</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.34487</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.47146</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.34134</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.35568</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.55161</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.55763</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.54634</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.5487799999999999</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.7507699999999999</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.7385900000000001</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.49891</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.6051</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.8696</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.53201</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.8538</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.7337899999999999</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.72651</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.79391</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.23211</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.59051</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.27634</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.8567400000000001</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.30137</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.56202</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.32209</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.5787899999999999</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.5396</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.72609</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.7091799999999999</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.74256</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.7559</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.75103</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.7282000000000001</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.7526499999999999</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.61781</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.7858099999999999</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.90952</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.86712</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.84868</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.78271</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.79044</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.79852</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.7452799999999999</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.8328</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.53975</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.5784900000000001</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.7765299999999999</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.78489</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.7788099999999999</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>1.10126</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.8582000000000001</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.17486</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.80841</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.90751</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.503</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.44335</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.37807</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1.52223</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1.22707</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.81986</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.5675800000000001</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.34101</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34216</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.38324</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.33228</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.32222</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.31275</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.31605</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.39694</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.5817599999999999</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32908</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33511</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.34772</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.33145</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.33419</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32525</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.33057</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.3285</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32648</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32793</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32605</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32084</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31974</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32636</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33023</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33517</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34592</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34243</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33691</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33872</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32611</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.33121</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33839</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.59915</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.60363</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33795</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.46551</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.37557</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.38773</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.38564</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.28982</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34229</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34173</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.29859</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32502</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.2818</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32948</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.32562</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32118</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.33019</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33355</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.3149</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32238</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32832</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32547</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.34563</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.38421</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.5147200000000001</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.68596</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.60897</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.52646</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.46768</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.37648</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.35224</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.39276</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.38364</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.3871</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.38193</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.41502</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36761</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36147</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36777</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36239</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37307</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36202</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39283</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38553</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37162</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40286</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35499</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.3694</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34933</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34931</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35128</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35537</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35135</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34938</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34623</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.35972</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34702</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34962</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36928</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34945</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34945</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32806</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.36303</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33643</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.36054</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.29336</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.33269</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32904</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32819</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.33033</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.32191</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.32198</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.32027</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.33555</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32579</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32963</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31878</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.33032</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.4709100000000001</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.35547</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.39187</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.80665</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.3876</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.35145</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.35695</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.36433</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33866</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33889</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.38111</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.56233</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.3891</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.38014</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.39791</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35134</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.37465</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34729</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36029</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36022</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36226</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.48234</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.40479</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.40642</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38363</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42968</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40916</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38571</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38502</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65195</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.83082</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47175</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.40085</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45942</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.3934</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35066</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35957</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34477</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.3127200000000001</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41075</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.3758</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37087</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36131</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35917</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35916</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36234</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35889</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36057</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35357</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35678</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35235</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35976</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.33974</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37945</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35814</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32988</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.32997</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.3567</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.28895</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.20707</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.39742</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.29508</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.29392</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.22495</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.33943</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.28819</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.29009</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.01784</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.32497</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.24723</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.29826</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.22128</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.32388</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.0335</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.34638</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.19013</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.31016</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.05991</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.28092</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.32536</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.45823</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.5076</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.56174</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>1.41415</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.49607</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.52561</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.99733</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.49177</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.9770700000000001</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.4241</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.37402</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.71034</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>1.49652</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.5682</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>1.03353</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.62909</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>1.49178</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>1.04555</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.93668</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.56375</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.61256</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.6164299999999999</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43004</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41895</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37805</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37448</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.3673</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36015</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34534</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.54635</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.75834</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.66864</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.93279</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41942</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.40518</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40493</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41136</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40904</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41775</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.40006</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39587</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41165</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40938</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39366</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38712</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.4185</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38727</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41663</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39008</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.3999</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.39986</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41249</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.39991</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45051</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44949</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.56059</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.5006499999999999</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45069</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.35297</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.41949</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.79865</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.8065399999999999</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.13666</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.20347</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.31422</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.42262</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.3591</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.2233</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.7007100000000001</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.7256</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.81979</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.5653400000000001</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.5555</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.5701000000000001</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.3751</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.34786</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>-0.01871</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>-0.02935</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.22623</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.29439</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>1.02726</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.75639</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.51564</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>1.09961</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.6017400000000001</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.5413300000000001</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.45438</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.61578</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.30896</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.46665</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.58651</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.36882</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.37168</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.41426</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.40423</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.4698</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.55241</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.45153</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.5243300000000001</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.43867</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.53873</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.58048</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.74849</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.69712</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.6474099999999999</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.64854</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.76711</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.0214</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.49032</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.14601</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.06569</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.81508</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.37598</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.8504400000000001</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.786</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6372100000000001</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>1.03628</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.6538200000000001</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.73315</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.59729</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.4784</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.47174</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41939</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.5516599999999999</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.39971</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.39958</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45813</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43679</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42655</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44836</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41782</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40083</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.4577</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39933</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40704</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39862</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38853</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37486</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37679</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37125</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38657</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39025</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37958</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36647</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36137</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.40973</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.40365</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.39127</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.43921</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39447</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38659</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36857</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.38264</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.4345</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.4243</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.43879</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.46585</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.58917</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.7087100000000001</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.30796</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.12071</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.16729</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.17799</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.37438</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.32725</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.02397</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30957</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29965</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.3132799999999999</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35262</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35494</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34876</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.36708</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.40769</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.40431</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.41816</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.43594</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.42116</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36372</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.41311</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41698</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.44836</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.42927</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.45396</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38084</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38627</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40612</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40201</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34409</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36549</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37798</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39922</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37947</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39963</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38081</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36026</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39388</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37906</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36415</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.50878</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.5176499999999999</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.46217</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.43075</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.38804</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37714</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35054</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37705</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.37356</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35628</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35515</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35122</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35747</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34738</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35075</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34859</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34037</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34046</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.3454700000000001</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33048</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33738</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33744</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.35155</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.32088</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31663</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32503</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.36663</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.33065</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.32441</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.25499</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.30533</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.27189</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.24917</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.26575</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.04216</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.19475</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.29474</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29737</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.07421</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.18216</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04336</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.27823</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.03172</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.18001</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.19074</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.06504</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31158</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.0221</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.24167</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.24958</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.17424</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23385</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27927</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.31777</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.27077</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.31445</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.33671</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.30468</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.36296</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34663</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.37011</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.42378</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.39291</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.35694</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.34514</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.41247</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.39734</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.3685</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.32067</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.41369</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.37031</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.42537</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.37771</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.39585</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.38856</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.39286</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.3687</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.38501</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.41464</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34778</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36513</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.36984</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.36579</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.3517</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32295</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.41257</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33842</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34431</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.34702</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33107</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32475</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31968</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31936</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.31028</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31062</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31096</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31097</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31088</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31659</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30682</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30682</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30931</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30989</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30615</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30682</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30741</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31137</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29676</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.25983</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.25357</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.1697</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.20889</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.45447</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.09268000000000001</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.07858</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.03825</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>0.02611</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.19101</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.03802000000000001</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>0.03742</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>0.0241</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>0.11325</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>0.19252</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>0.12316</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>0.05086</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>0.03945000000000001</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0.03722</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>0.11174</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0.02228</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.02928</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>0.02479</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>0.02243</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0.03181</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.09353</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.05996</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>0.02207</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>0.02489</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>0.02208</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>0.02136</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.03456</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>0.0253</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>0.06126</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>0.04157</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.17197</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.20854</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.25335</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.29444</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.2752</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.2797</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.27233</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.27738</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.29017</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.31185</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.29469</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.29792</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.28579</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.31254</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.30304</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.30474</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.29416</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.30632</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.29356</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.30836</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.29831</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.32489</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.45935</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.31704</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.33484</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.30552</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.28143</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.28918</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.27701</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.26787</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.22939</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.13532</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29997</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.5417799999999999</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.28206</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.16924</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.32052</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.28176</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.31843</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.25885</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.3129</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.29236</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.27972</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.26073</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.24355</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.23136</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.24881</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.25503</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.21988</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.25594</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.24749</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.26081</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.27051</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.24834</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.28806</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.26366</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.30363</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.4079100000000001</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.30456</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.27535</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.22551</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.15021</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.6213099999999999</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.6242799999999999</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.73487</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.58143</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.30448</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.47684</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.16277</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.2716</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.15273</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.12499</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>1.11215</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.1599</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.28054</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.14983</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.31476</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.12012</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.01081</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.12832</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.18532</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.05713</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.20158</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.03665</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.14309</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.29455</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.24085</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.09099</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.18485</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.32403</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.511</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.17501</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.40443</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.3933</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.5254800000000001</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.47993</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.49643</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.49704</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.49653</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.53907</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.41892</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.51707</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.4337</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.54011</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.94532</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.69255</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.67749</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.71611</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.83927</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.6929999999999999</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.72188</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.73451</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.83568</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.55911</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.51001</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.5512999999999999</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.5502999999999999</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.6624</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.56908</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.47857</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.34615</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.34107</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.41687</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32913</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.39712</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.45792</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.38441</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.42356</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.37833</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.35962</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.35758</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.34924</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.35778</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.34206</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34499</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.14299</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.33821</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.33484</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.3277</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.33429</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.33955</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.34886</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.34849</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.35928</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.9647100000000001</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.7636900000000001</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.6663600000000001</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.61542</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.49528</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.5836399999999999</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.50102</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.43887</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1.09086</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.62786</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.54032</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.63081</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.70624</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.70084</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.55147</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.56921</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.45245</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.36511</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.36428</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.4145</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.32663</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.16296</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.36769</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.28598</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.36538</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.22679</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.38952</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.57737</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.33208</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.16806</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.35881</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.33341</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.34962</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.35093</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.35866</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.36985</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.37636</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.39062</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.39561</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.38783</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.39444</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.37221</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.37971</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.35411</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.38836</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.40567</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.39614</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.43052</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.55274</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.54701</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.43179</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.36951</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.7683099999999999</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.49473</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.49029</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.56032</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.53098</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.41087</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.41266</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.4012</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.38295</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.3894</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.32981</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.34554</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.33005</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33352</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.3335</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37038</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.36453</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.35918</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.3088399999999999</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.34061</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.34029</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.34886</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.33602</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.34413</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34782</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.3118</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34338</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.34498</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32965</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32918</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33496</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34651</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33586</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34233</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35556</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32739</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36911</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35673</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.37327</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35941</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.42909</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.5554600000000001</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.34657</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.43675</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.54706</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.78013</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.70162</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.9278200000000001</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.02925</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.39283</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.5043800000000001</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.54095</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.48696</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.4605</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.49428</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.47319</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.46184</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>1.32687</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.46501</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.32336</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.6338400000000001</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.35706</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.45628</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.36172</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.4843</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.48368</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.14552</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.46551</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.4156</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.47615</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.5008</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.49472</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.53687</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.64823</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.6708099999999999</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.71768</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.7842100000000001</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.76739</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.83741</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.84988</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.82762</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.7044</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.6079600000000001</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.59128</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.47189</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.71116</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.54461</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.61815</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.54383</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.57499</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.5510900000000001</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.51613</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.5378999999999999</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42414</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.68335</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.50308</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40147</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45845</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.46103</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38015</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.50484</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.4765</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.32119</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.3727</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36266</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36867</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.5637799999999999</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.4012</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40125</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39192</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37554</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37441</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37864</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37729</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36915</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36691</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36152</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36039</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35586</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32883</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35618</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37102</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39958</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37575</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36966</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.37699</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.39402</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.47134</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.39146</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.6082799999999999</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.60162</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.58801</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.6580900000000001</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.66688</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.57145</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.7326699999999999</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.8029500000000001</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.5231</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.33938</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.52324</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.45014</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.53139</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.51413</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.51425</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.24387</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.24024</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.25894</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.49121</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.45585</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.3246</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.34212</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.43182</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.20208</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.48057</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.55586</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.5396599999999999</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.43064</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.61874</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.6210800000000001</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.42358</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.64202</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.42717</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.40879</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.44072</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.74733</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.67175</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.6113</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.5920299999999999</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.46968</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.5432</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.50602</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.50652</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.4624</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.5531</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.53628</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.26654</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.67962</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.53942</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.47597</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.45416</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.30416</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.7309600000000001</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.49775</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.49953</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39829</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.50299</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.48093</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.44466</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.38327</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36944</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37505</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27076</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.37121</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37038</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.34035</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.34063</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34984</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32783</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33933</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.41112</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.3421</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34082</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.36289</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.34255</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.34133</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.34202</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.32143</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.33234</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.32623</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.31655</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.31845</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.30904</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.30633</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.38645</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.31982</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.30483</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.29987</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.29564</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.28904</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.32873</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.36171</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.4535</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.40985</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.36601</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.5842200000000001</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.49097</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.78142</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.27027</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.19924</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.15747</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.77442</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.6768200000000001</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.20057</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.09181</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.004070000000000001</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.10901</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.09381</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.24921</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.01082</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.21885</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.09498999999999999</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.22368</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.34167</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.20921</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.14294</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.31961</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.31943</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.24933</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.51642</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.51318</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.39365</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.36736</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.32278</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.45963</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.53495</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.5866</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.4616</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.47459</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.3869</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.45607</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.46667</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.15431</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.01394</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.26495</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.28397</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.40687</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.31068</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.42932</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.52538</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.50573</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.51162</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.5414500000000001</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.52677</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.5085500000000001</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.63632</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.48337</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.50229</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.45283</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.43864</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.38602</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.37822</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37529</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.00799</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.5173300000000001</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.5714199999999999</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.62336</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.47381</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.36171</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.38748</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.36218</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38501</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.35602</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34884</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37864</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35912</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.36571</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38014</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.35589</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.36281</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36394</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.36353</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.3658</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35919</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36595</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.38343</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.34554</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.41733</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.31514</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.31505</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.30956</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.38927</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.42638</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.41254</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.39339</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.41911</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.38411</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.42463</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.5688799999999999</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.33004</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.30924</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.35531</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.34778</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.25632</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.45363</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.28496</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.09187000000000001</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.07998999999999999</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.13804</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.09025</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.17951</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.50212</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.23391</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.29767</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.40511</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.20279</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.28777</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.34316</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>1.13972</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.8974099999999999</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.36703</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.8438300000000001</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.43569</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.7499400000000001</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>1.13507</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1.21725</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>1.01208</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.8438099999999999</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.5805399999999999</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.50658</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.7912899999999999</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.8035599999999999</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.5438099999999999</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.7840499999999999</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.56237</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.59692</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.58713</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.57401</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.80079</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.6439900000000001</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.64776</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.6590199999999999</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.7868200000000001</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.54038</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.56368</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.5137699999999999</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.5846</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.71494</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.7736799999999999</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.56329</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.43686</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.41174</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.40656</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.33486</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.67714</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.44333</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.44623</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.34236</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.39055</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.38503</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.38297</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.36958</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41964</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.36475</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.39048</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37332</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.35562</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.35442</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33352</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.32777</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32477</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.33493</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34257</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.36346</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34731</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.34606</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.33333</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.31769</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.28157</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.25879</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.24125</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17151</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.22496</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.31139</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.27286</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.25783</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.37512</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.31437</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.24315</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.19658</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.23869</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.23393</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.21636</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.14528</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.15722</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.20656</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.15347</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.20058</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.16364</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.27401</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.2319</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.18339</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.12161</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.34604</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.20131</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.22433</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.28045</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.21568</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.49404</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.31644</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.31702</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.35674</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.39318</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.35076</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.36468</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.38634</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.38905</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.39238</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.40555</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.45276</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.47589</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.42521</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.43893</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.34694</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.34692</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.5231699999999999</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.3444</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.46787</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.45569</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.43024</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.43865</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.54401</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.56324</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.51376</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.44558</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.45043</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.42439</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.40578</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40849</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40967</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38407</v>
       </c>
     </row>
   </sheetData>
